--- a/resource/task2.xlsx
+++ b/resource/task2.xlsx
@@ -57,14 +57,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -520,28 +513,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -550,118 +546,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -30378,7 +30371,7 @@
         <v>4</v>
       </c>
       <c r="C1729">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1729">
         <v>13</v>
@@ -30395,7 +30388,7 @@
         <v>4</v>
       </c>
       <c r="C1730">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1730">
         <v>13</v>
@@ -30412,7 +30405,7 @@
         <v>4</v>
       </c>
       <c r="C1731">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1731">
         <v>13</v>
@@ -30429,7 +30422,7 @@
         <v>4</v>
       </c>
       <c r="C1732">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1732">
         <v>13</v>
@@ -30446,7 +30439,7 @@
         <v>4</v>
       </c>
       <c r="C1733">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1733">
         <v>13</v>
@@ -30463,7 +30456,7 @@
         <v>4</v>
       </c>
       <c r="C1734">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1734">
         <v>13</v>
@@ -30480,7 +30473,7 @@
         <v>4</v>
       </c>
       <c r="C1735">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1735">
         <v>13</v>
@@ -30497,7 +30490,7 @@
         <v>4</v>
       </c>
       <c r="C1736">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1736">
         <v>13</v>
@@ -30531,7 +30524,7 @@
         <v>5</v>
       </c>
       <c r="C1738">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1738">
         <v>13</v>
@@ -30548,7 +30541,7 @@
         <v>5</v>
       </c>
       <c r="C1739">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1739">
         <v>13</v>
@@ -30565,7 +30558,7 @@
         <v>5</v>
       </c>
       <c r="C1740">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1740">
         <v>13</v>
@@ -30582,7 +30575,7 @@
         <v>5</v>
       </c>
       <c r="C1741">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1741">
         <v>13</v>
@@ -30599,7 +30592,7 @@
         <v>5</v>
       </c>
       <c r="C1742">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1742">
         <v>13</v>
@@ -30616,7 +30609,7 @@
         <v>5</v>
       </c>
       <c r="C1743">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1743">
         <v>13</v>
@@ -30633,7 +30626,7 @@
         <v>5</v>
       </c>
       <c r="C1744">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1744">
         <v>13</v>
@@ -30650,7 +30643,7 @@
         <v>5</v>
       </c>
       <c r="C1745">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1745">
         <v>13</v>
@@ -31245,7 +31238,7 @@
         <v>10</v>
       </c>
       <c r="C1780">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1780">
         <v>13</v>
@@ -31262,7 +31255,7 @@
         <v>10</v>
       </c>
       <c r="C1781">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1781">
         <v>13</v>
@@ -31279,7 +31272,7 @@
         <v>10</v>
       </c>
       <c r="C1782">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1782">
         <v>13</v>
@@ -31296,7 +31289,7 @@
         <v>10</v>
       </c>
       <c r="C1783">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1783">
         <v>13</v>
@@ -31313,7 +31306,7 @@
         <v>10</v>
       </c>
       <c r="C1784">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1784">
         <v>13</v>
@@ -31330,7 +31323,7 @@
         <v>10</v>
       </c>
       <c r="C1785">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1785">
         <v>13</v>
@@ -31347,7 +31340,7 @@
         <v>10</v>
       </c>
       <c r="C1786">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1786">
         <v>13</v>
@@ -31364,7 +31357,7 @@
         <v>10</v>
       </c>
       <c r="C1787">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1787">
         <v>13</v>
@@ -32163,7 +32156,7 @@
         <v>15</v>
       </c>
       <c r="C1834">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1834">
         <v>13</v>
@@ -32180,7 +32173,7 @@
         <v>15</v>
       </c>
       <c r="C1835">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1835">
         <v>13</v>
@@ -32197,7 +32190,7 @@
         <v>15</v>
       </c>
       <c r="C1836">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1836">
         <v>13</v>
@@ -32214,7 +32207,7 @@
         <v>15</v>
       </c>
       <c r="C1837">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1837">
         <v>13</v>
@@ -32231,7 +32224,7 @@
         <v>15</v>
       </c>
       <c r="C1838">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1838">
         <v>13</v>
@@ -32248,7 +32241,7 @@
         <v>15</v>
       </c>
       <c r="C1839">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1839">
         <v>13</v>
@@ -32265,7 +32258,7 @@
         <v>15</v>
       </c>
       <c r="C1840">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1840">
         <v>13</v>
@@ -32282,7 +32275,7 @@
         <v>15</v>
       </c>
       <c r="C1841">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1841">
         <v>13</v>
@@ -33268,7 +33261,7 @@
         <v>21</v>
       </c>
       <c r="C1899">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1899">
         <v>13</v>
@@ -33285,7 +33278,7 @@
         <v>21</v>
       </c>
       <c r="C1900">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1900">
         <v>13</v>
@@ -33302,7 +33295,7 @@
         <v>21</v>
       </c>
       <c r="C1901">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1901">
         <v>13</v>
@@ -33319,7 +33312,7 @@
         <v>21</v>
       </c>
       <c r="C1902">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1902">
         <v>13</v>
@@ -33336,7 +33329,7 @@
         <v>21</v>
       </c>
       <c r="C1903">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1903">
         <v>13</v>
@@ -33353,7 +33346,7 @@
         <v>21</v>
       </c>
       <c r="C1904">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1904">
         <v>13</v>
@@ -33370,7 +33363,7 @@
         <v>21</v>
       </c>
       <c r="C1905">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1905">
         <v>13</v>
@@ -33387,7 +33380,7 @@
         <v>21</v>
       </c>
       <c r="C1906">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1906">
         <v>13</v>
@@ -33438,7 +33431,7 @@
         <v>22</v>
       </c>
       <c r="C1909">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1909">
         <v>13</v>
@@ -33455,7 +33448,7 @@
         <v>22</v>
       </c>
       <c r="C1910">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1910">
         <v>13</v>
@@ -33472,7 +33465,7 @@
         <v>22</v>
       </c>
       <c r="C1911">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1911">
         <v>13</v>
@@ -33489,7 +33482,7 @@
         <v>22</v>
       </c>
       <c r="C1912">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1912">
         <v>13</v>
@@ -33506,7 +33499,7 @@
         <v>22</v>
       </c>
       <c r="C1913">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1913">
         <v>13</v>
@@ -33523,7 +33516,7 @@
         <v>22</v>
       </c>
       <c r="C1914">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1914">
         <v>13</v>
@@ -33540,7 +33533,7 @@
         <v>22</v>
       </c>
       <c r="C1915">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1915">
         <v>13</v>
@@ -33557,7 +33550,7 @@
         <v>22</v>
       </c>
       <c r="C1916">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1916">
         <v>13</v>
@@ -33608,7 +33601,7 @@
         <v>23</v>
       </c>
       <c r="C1919">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1919">
         <v>13</v>
@@ -33625,7 +33618,7 @@
         <v>23</v>
       </c>
       <c r="C1920">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1920">
         <v>13</v>
@@ -33642,7 +33635,7 @@
         <v>23</v>
       </c>
       <c r="C1921">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1921">
         <v>13</v>
@@ -33659,7 +33652,7 @@
         <v>23</v>
       </c>
       <c r="C1922">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1922">
         <v>13</v>
@@ -33676,7 +33669,7 @@
         <v>23</v>
       </c>
       <c r="C1923">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1923">
         <v>13</v>
@@ -33693,7 +33686,7 @@
         <v>23</v>
       </c>
       <c r="C1924">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1924">
         <v>13</v>
@@ -33710,7 +33703,7 @@
         <v>23</v>
       </c>
       <c r="C1925">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1925">
         <v>13</v>
@@ -33727,7 +33720,7 @@
         <v>23</v>
       </c>
       <c r="C1926">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1926">
         <v>13</v>
@@ -33778,7 +33771,7 @@
         <v>24</v>
       </c>
       <c r="C1929">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1929">
         <v>13</v>
@@ -33795,7 +33788,7 @@
         <v>24</v>
       </c>
       <c r="C1930">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1930">
         <v>13</v>
@@ -33812,7 +33805,7 @@
         <v>24</v>
       </c>
       <c r="C1931">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1931">
         <v>13</v>
@@ -33829,7 +33822,7 @@
         <v>24</v>
       </c>
       <c r="C1932">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1932">
         <v>13</v>
@@ -33846,7 +33839,7 @@
         <v>24</v>
       </c>
       <c r="C1933">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1933">
         <v>13</v>
@@ -33863,7 +33856,7 @@
         <v>24</v>
       </c>
       <c r="C1934">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1934">
         <v>13</v>
@@ -33880,7 +33873,7 @@
         <v>24</v>
       </c>
       <c r="C1935">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1935">
         <v>13</v>
@@ -33897,7 +33890,7 @@
         <v>24</v>
       </c>
       <c r="C1936">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1936">
         <v>13</v>
@@ -33948,7 +33941,7 @@
         <v>25</v>
       </c>
       <c r="C1939">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1939">
         <v>13</v>
@@ -33965,7 +33958,7 @@
         <v>25</v>
       </c>
       <c r="C1940">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1940">
         <v>13</v>
@@ -33982,7 +33975,7 @@
         <v>25</v>
       </c>
       <c r="C1941">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1941">
         <v>13</v>
@@ -33999,7 +33992,7 @@
         <v>25</v>
       </c>
       <c r="C1942">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1942">
         <v>13</v>
@@ -34016,7 +34009,7 @@
         <v>25</v>
       </c>
       <c r="C1943">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1943">
         <v>13</v>
@@ -34033,7 +34026,7 @@
         <v>25</v>
       </c>
       <c r="C1944">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1944">
         <v>13</v>
@@ -34050,7 +34043,7 @@
         <v>25</v>
       </c>
       <c r="C1945">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1945">
         <v>13</v>
@@ -34067,7 +34060,7 @@
         <v>25</v>
       </c>
       <c r="C1946">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1946">
         <v>13</v>
@@ -34118,7 +34111,7 @@
         <v>26</v>
       </c>
       <c r="C1949">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D1949">
         <v>13</v>
@@ -34135,7 +34128,7 @@
         <v>26</v>
       </c>
       <c r="C1950">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1950">
         <v>13</v>
@@ -34152,7 +34145,7 @@
         <v>26</v>
       </c>
       <c r="C1951">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1951">
         <v>13</v>
@@ -34169,7 +34162,7 @@
         <v>26</v>
       </c>
       <c r="C1952">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1952">
         <v>13</v>
@@ -34186,7 +34179,7 @@
         <v>26</v>
       </c>
       <c r="C1953">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1953">
         <v>13</v>
@@ -34203,7 +34196,7 @@
         <v>26</v>
       </c>
       <c r="C1954">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1954">
         <v>13</v>
@@ -34220,7 +34213,7 @@
         <v>26</v>
       </c>
       <c r="C1955">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1955">
         <v>13</v>
@@ -34237,7 +34230,7 @@
         <v>26</v>
       </c>
       <c r="C1956">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D1956">
         <v>13</v>
@@ -35223,7 +35216,7 @@
         <v>32</v>
       </c>
       <c r="C2014">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2014">
         <v>13</v>
@@ -35240,7 +35233,7 @@
         <v>32</v>
       </c>
       <c r="C2015">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2015">
         <v>13</v>
@@ -35257,7 +35250,7 @@
         <v>32</v>
       </c>
       <c r="C2016">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2016">
         <v>13</v>
@@ -35274,7 +35267,7 @@
         <v>32</v>
       </c>
       <c r="C2017">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2017">
         <v>13</v>
@@ -35291,7 +35284,7 @@
         <v>32</v>
       </c>
       <c r="C2018">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2018">
         <v>13</v>
@@ -35308,7 +35301,7 @@
         <v>32</v>
       </c>
       <c r="C2019">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2019">
         <v>13</v>
@@ -35325,7 +35318,7 @@
         <v>32</v>
       </c>
       <c r="C2020">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2020">
         <v>13</v>
@@ -35342,7 +35335,7 @@
         <v>32</v>
       </c>
       <c r="C2021">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2021">
         <v>13</v>
@@ -35376,7 +35369,7 @@
         <v>33</v>
       </c>
       <c r="C2023">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2023">
         <v>13</v>
@@ -35393,7 +35386,7 @@
         <v>33</v>
       </c>
       <c r="C2024">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2024">
         <v>13</v>
@@ -35410,7 +35403,7 @@
         <v>33</v>
       </c>
       <c r="C2025">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2025">
         <v>13</v>
@@ -35427,7 +35420,7 @@
         <v>33</v>
       </c>
       <c r="C2026">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2026">
         <v>13</v>
@@ -35444,7 +35437,7 @@
         <v>33</v>
       </c>
       <c r="C2027">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2027">
         <v>13</v>
@@ -35461,7 +35454,7 @@
         <v>33</v>
       </c>
       <c r="C2028">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2028">
         <v>13</v>
@@ -35478,7 +35471,7 @@
         <v>33</v>
       </c>
       <c r="C2029">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2029">
         <v>13</v>
@@ -35495,7 +35488,7 @@
         <v>33</v>
       </c>
       <c r="C2030">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2030">
         <v>13</v>
@@ -36090,7 +36083,7 @@
         <v>37</v>
       </c>
       <c r="C2065">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2065">
         <v>13</v>
@@ -36107,7 +36100,7 @@
         <v>37</v>
       </c>
       <c r="C2066">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2066">
         <v>13</v>
@@ -36124,7 +36117,7 @@
         <v>37</v>
       </c>
       <c r="C2067">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2067">
         <v>13</v>
@@ -36141,7 +36134,7 @@
         <v>37</v>
       </c>
       <c r="C2068">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2068">
         <v>13</v>
@@ -36158,7 +36151,7 @@
         <v>37</v>
       </c>
       <c r="C2069">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2069">
         <v>13</v>
@@ -36175,7 +36168,7 @@
         <v>37</v>
       </c>
       <c r="C2070">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2070">
         <v>13</v>
@@ -36192,7 +36185,7 @@
         <v>37</v>
       </c>
       <c r="C2071">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2071">
         <v>13</v>
@@ -36209,7 +36202,7 @@
         <v>37</v>
       </c>
       <c r="C2072">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2072">
         <v>13</v>
@@ -36260,7 +36253,7 @@
         <v>38</v>
       </c>
       <c r="C2075">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2075">
         <v>13</v>
@@ -36277,7 +36270,7 @@
         <v>38</v>
       </c>
       <c r="C2076">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2076">
         <v>13</v>
@@ -36294,7 +36287,7 @@
         <v>38</v>
       </c>
       <c r="C2077">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2077">
         <v>13</v>
@@ -36311,7 +36304,7 @@
         <v>38</v>
       </c>
       <c r="C2078">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2078">
         <v>13</v>
@@ -36328,7 +36321,7 @@
         <v>38</v>
       </c>
       <c r="C2079">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2079">
         <v>13</v>
@@ -36345,7 +36338,7 @@
         <v>38</v>
       </c>
       <c r="C2080">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2080">
         <v>13</v>
@@ -36362,7 +36355,7 @@
         <v>38</v>
       </c>
       <c r="C2081">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2081">
         <v>13</v>
@@ -36379,7 +36372,7 @@
         <v>38</v>
       </c>
       <c r="C2082">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2082">
         <v>13</v>
@@ -37178,7 +37171,7 @@
         <v>43</v>
       </c>
       <c r="C2129">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2129">
         <v>41</v>
@@ -37195,7 +37188,7 @@
         <v>43</v>
       </c>
       <c r="C2130">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2130">
         <v>41</v>
@@ -37212,7 +37205,7 @@
         <v>43</v>
       </c>
       <c r="C2131">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2131">
         <v>41</v>
@@ -37229,7 +37222,7 @@
         <v>43</v>
       </c>
       <c r="C2132">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2132">
         <v>41</v>
@@ -37246,7 +37239,7 @@
         <v>43</v>
       </c>
       <c r="C2133">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2133">
         <v>41</v>
@@ -37263,7 +37256,7 @@
         <v>43</v>
       </c>
       <c r="C2134">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2134">
         <v>41</v>
@@ -37280,7 +37273,7 @@
         <v>43</v>
       </c>
       <c r="C2135">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2135">
         <v>41</v>
@@ -37297,7 +37290,7 @@
         <v>43</v>
       </c>
       <c r="C2136">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2136">
         <v>41</v>
@@ -38096,7 +38089,7 @@
         <v>48</v>
       </c>
       <c r="C2183">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2183">
         <v>41</v>
@@ -38113,7 +38106,7 @@
         <v>48</v>
       </c>
       <c r="C2184">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2184">
         <v>41</v>
@@ -38130,7 +38123,7 @@
         <v>48</v>
       </c>
       <c r="C2185">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2185">
         <v>41</v>
@@ -38147,7 +38140,7 @@
         <v>48</v>
       </c>
       <c r="C2186">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2186">
         <v>41</v>
@@ -38164,7 +38157,7 @@
         <v>48</v>
       </c>
       <c r="C2187">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2187">
         <v>41</v>
@@ -38181,7 +38174,7 @@
         <v>48</v>
       </c>
       <c r="C2188">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2188">
         <v>41</v>
@@ -38198,7 +38191,7 @@
         <v>48</v>
       </c>
       <c r="C2189">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2189">
         <v>41</v>
@@ -38215,7 +38208,7 @@
         <v>48</v>
       </c>
       <c r="C2190">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2190">
         <v>41</v>
@@ -38266,7 +38259,7 @@
         <v>49</v>
       </c>
       <c r="C2193">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2193">
         <v>41</v>
@@ -38283,7 +38276,7 @@
         <v>49</v>
       </c>
       <c r="C2194">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2194">
         <v>41</v>
@@ -38300,7 +38293,7 @@
         <v>49</v>
       </c>
       <c r="C2195">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2195">
         <v>41</v>
@@ -38317,7 +38310,7 @@
         <v>49</v>
       </c>
       <c r="C2196">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2196">
         <v>41</v>
@@ -38334,7 +38327,7 @@
         <v>49</v>
       </c>
       <c r="C2197">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2197">
         <v>41</v>
@@ -38351,7 +38344,7 @@
         <v>49</v>
       </c>
       <c r="C2198">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2198">
         <v>41</v>
@@ -38368,7 +38361,7 @@
         <v>49</v>
       </c>
       <c r="C2199">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2199">
         <v>41</v>
@@ -38385,7 +38378,7 @@
         <v>49</v>
       </c>
       <c r="C2200">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2200">
         <v>41</v>
@@ -38997,7 +38990,7 @@
         <v>53</v>
       </c>
       <c r="C2236">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2236">
         <v>41</v>
@@ -39014,7 +39007,7 @@
         <v>53</v>
       </c>
       <c r="C2237">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2237">
         <v>41</v>
@@ -39031,7 +39024,7 @@
         <v>53</v>
       </c>
       <c r="C2238">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2238">
         <v>41</v>
@@ -39048,7 +39041,7 @@
         <v>53</v>
       </c>
       <c r="C2239">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2239">
         <v>41</v>
@@ -39065,7 +39058,7 @@
         <v>53</v>
       </c>
       <c r="C2240">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2240">
         <v>41</v>
@@ -39082,7 +39075,7 @@
         <v>53</v>
       </c>
       <c r="C2241">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2241">
         <v>41</v>
@@ -39099,7 +39092,7 @@
         <v>53</v>
       </c>
       <c r="C2242">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2242">
         <v>41</v>
@@ -39116,7 +39109,7 @@
         <v>53</v>
       </c>
       <c r="C2243">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2243">
         <v>41</v>
@@ -39167,7 +39160,7 @@
         <v>54</v>
       </c>
       <c r="C2246">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2246">
         <v>41</v>
@@ -39184,7 +39177,7 @@
         <v>54</v>
       </c>
       <c r="C2247">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2247">
         <v>41</v>
@@ -39201,7 +39194,7 @@
         <v>54</v>
       </c>
       <c r="C2248">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2248">
         <v>41</v>
@@ -39218,7 +39211,7 @@
         <v>54</v>
       </c>
       <c r="C2249">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2249">
         <v>41</v>
@@ -39235,7 +39228,7 @@
         <v>54</v>
       </c>
       <c r="C2250">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2250">
         <v>41</v>
@@ -39252,7 +39245,7 @@
         <v>54</v>
       </c>
       <c r="C2251">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2251">
         <v>41</v>
@@ -39269,7 +39262,7 @@
         <v>54</v>
       </c>
       <c r="C2252">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2252">
         <v>41</v>
@@ -39286,7 +39279,7 @@
         <v>54</v>
       </c>
       <c r="C2253">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2253">
         <v>41</v>
@@ -39337,7 +39330,7 @@
         <v>55</v>
       </c>
       <c r="C2256">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2256">
         <v>41</v>
@@ -39354,7 +39347,7 @@
         <v>55</v>
       </c>
       <c r="C2257">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2257">
         <v>41</v>
@@ -39371,7 +39364,7 @@
         <v>55</v>
       </c>
       <c r="C2258">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2258">
         <v>41</v>
@@ -39388,7 +39381,7 @@
         <v>55</v>
       </c>
       <c r="C2259">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2259">
         <v>41</v>
@@ -39405,7 +39398,7 @@
         <v>55</v>
       </c>
       <c r="C2260">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2260">
         <v>41</v>
@@ -39422,7 +39415,7 @@
         <v>55</v>
       </c>
       <c r="C2261">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2261">
         <v>41</v>
@@ -39439,7 +39432,7 @@
         <v>55</v>
       </c>
       <c r="C2262">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2262">
         <v>41</v>
@@ -39456,7 +39449,7 @@
         <v>55</v>
       </c>
       <c r="C2263">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2263">
         <v>41</v>
@@ -39507,7 +39500,7 @@
         <v>56</v>
       </c>
       <c r="C2266">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2266">
         <v>41</v>
@@ -39524,7 +39517,7 @@
         <v>56</v>
       </c>
       <c r="C2267">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2267">
         <v>41</v>
@@ -39541,7 +39534,7 @@
         <v>56</v>
       </c>
       <c r="C2268">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2268">
         <v>41</v>
@@ -39558,7 +39551,7 @@
         <v>56</v>
       </c>
       <c r="C2269">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2269">
         <v>41</v>
@@ -39575,7 +39568,7 @@
         <v>56</v>
       </c>
       <c r="C2270">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2270">
         <v>41</v>
@@ -39592,7 +39585,7 @@
         <v>56</v>
       </c>
       <c r="C2271">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2271">
         <v>41</v>
@@ -39609,7 +39602,7 @@
         <v>56</v>
       </c>
       <c r="C2272">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2272">
         <v>41</v>
@@ -39626,7 +39619,7 @@
         <v>56</v>
       </c>
       <c r="C2273">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2273">
         <v>41</v>
@@ -39677,7 +39670,7 @@
         <v>57</v>
       </c>
       <c r="C2276">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2276">
         <v>41</v>
@@ -39694,7 +39687,7 @@
         <v>57</v>
       </c>
       <c r="C2277">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2277">
         <v>41</v>
@@ -39711,7 +39704,7 @@
         <v>57</v>
       </c>
       <c r="C2278">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2278">
         <v>41</v>
@@ -39728,7 +39721,7 @@
         <v>57</v>
       </c>
       <c r="C2279">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2279">
         <v>41</v>
@@ -39745,7 +39738,7 @@
         <v>57</v>
       </c>
       <c r="C2280">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2280">
         <v>41</v>
@@ -39762,7 +39755,7 @@
         <v>57</v>
       </c>
       <c r="C2281">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2281">
         <v>41</v>
@@ -39779,7 +39772,7 @@
         <v>57</v>
       </c>
       <c r="C2282">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2282">
         <v>41</v>
@@ -39796,7 +39789,7 @@
         <v>57</v>
       </c>
       <c r="C2283">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2283">
         <v>41</v>
@@ -39847,7 +39840,7 @@
         <v>58</v>
       </c>
       <c r="C2286">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2286">
         <v>41</v>
@@ -39864,7 +39857,7 @@
         <v>58</v>
       </c>
       <c r="C2287">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2287">
         <v>41</v>
@@ -39881,7 +39874,7 @@
         <v>58</v>
       </c>
       <c r="C2288">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2288">
         <v>41</v>
@@ -39898,7 +39891,7 @@
         <v>58</v>
       </c>
       <c r="C2289">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2289">
         <v>41</v>
@@ -39915,7 +39908,7 @@
         <v>58</v>
       </c>
       <c r="C2290">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2290">
         <v>41</v>
@@ -39932,7 +39925,7 @@
         <v>58</v>
       </c>
       <c r="C2291">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2291">
         <v>41</v>
@@ -39949,7 +39942,7 @@
         <v>58</v>
       </c>
       <c r="C2292">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2292">
         <v>41</v>
@@ -39966,7 +39959,7 @@
         <v>58</v>
       </c>
       <c r="C2293">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2293">
         <v>41</v>
@@ -40017,7 +40010,7 @@
         <v>59</v>
       </c>
       <c r="C2296">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2296">
         <v>41</v>
@@ -40034,7 +40027,7 @@
         <v>59</v>
       </c>
       <c r="C2297">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2297">
         <v>41</v>
@@ -40051,7 +40044,7 @@
         <v>59</v>
       </c>
       <c r="C2298">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2298">
         <v>41</v>
@@ -40068,7 +40061,7 @@
         <v>59</v>
       </c>
       <c r="C2299">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2299">
         <v>41</v>
@@ -40085,7 +40078,7 @@
         <v>59</v>
       </c>
       <c r="C2300">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2300">
         <v>41</v>
@@ -40102,7 +40095,7 @@
         <v>59</v>
       </c>
       <c r="C2301">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2301">
         <v>41</v>
@@ -40119,7 +40112,7 @@
         <v>59</v>
       </c>
       <c r="C2302">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2302">
         <v>41</v>
@@ -40136,7 +40129,7 @@
         <v>59</v>
       </c>
       <c r="C2303">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2303">
         <v>41</v>
@@ -40187,7 +40180,7 @@
         <v>60</v>
       </c>
       <c r="C2306">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2306">
         <v>41</v>
@@ -40204,7 +40197,7 @@
         <v>60</v>
       </c>
       <c r="C2307">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2307">
         <v>41</v>
@@ -40221,7 +40214,7 @@
         <v>60</v>
       </c>
       <c r="C2308">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2308">
         <v>41</v>
@@ -40238,7 +40231,7 @@
         <v>60</v>
       </c>
       <c r="C2309">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2309">
         <v>41</v>
@@ -40255,7 +40248,7 @@
         <v>60</v>
       </c>
       <c r="C2310">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2310">
         <v>41</v>
@@ -40272,7 +40265,7 @@
         <v>60</v>
       </c>
       <c r="C2311">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2311">
         <v>41</v>
@@ -40289,7 +40282,7 @@
         <v>60</v>
       </c>
       <c r="C2312">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2312">
         <v>41</v>
@@ -40306,7 +40299,7 @@
         <v>60</v>
       </c>
       <c r="C2313">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2313">
         <v>41</v>
@@ -41105,7 +41098,7 @@
         <v>65</v>
       </c>
       <c r="C2360">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2360">
         <v>41</v>
@@ -41122,7 +41115,7 @@
         <v>65</v>
       </c>
       <c r="C2361">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2361">
         <v>41</v>
@@ -41139,7 +41132,7 @@
         <v>65</v>
       </c>
       <c r="C2362">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2362">
         <v>41</v>
@@ -41156,7 +41149,7 @@
         <v>65</v>
       </c>
       <c r="C2363">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2363">
         <v>41</v>
@@ -41173,7 +41166,7 @@
         <v>65</v>
       </c>
       <c r="C2364">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2364">
         <v>41</v>
@@ -41190,7 +41183,7 @@
         <v>65</v>
       </c>
       <c r="C2365">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2365">
         <v>41</v>
@@ -41207,7 +41200,7 @@
         <v>65</v>
       </c>
       <c r="C2366">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2366">
         <v>41</v>
@@ -41224,7 +41217,7 @@
         <v>65</v>
       </c>
       <c r="C2367">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2367">
         <v>41</v>
@@ -42210,7 +42203,7 @@
         <v>71</v>
       </c>
       <c r="C2425">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2425">
         <v>41</v>
@@ -42227,7 +42220,7 @@
         <v>71</v>
       </c>
       <c r="C2426">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2426">
         <v>41</v>
@@ -42244,7 +42237,7 @@
         <v>71</v>
       </c>
       <c r="C2427">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2427">
         <v>41</v>
@@ -42261,7 +42254,7 @@
         <v>71</v>
       </c>
       <c r="C2428">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2428">
         <v>41</v>
@@ -42278,7 +42271,7 @@
         <v>71</v>
       </c>
       <c r="C2429">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2429">
         <v>41</v>
@@ -42295,7 +42288,7 @@
         <v>71</v>
       </c>
       <c r="C2430">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2430">
         <v>41</v>
@@ -42312,7 +42305,7 @@
         <v>71</v>
       </c>
       <c r="C2431">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2431">
         <v>41</v>
@@ -42329,7 +42322,7 @@
         <v>71</v>
       </c>
       <c r="C2432">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2432">
         <v>41</v>
@@ -42941,7 +42934,7 @@
         <v>76</v>
       </c>
       <c r="C2468">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2468">
         <v>41</v>
@@ -42958,7 +42951,7 @@
         <v>76</v>
       </c>
       <c r="C2469">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2469">
         <v>41</v>
@@ -42975,7 +42968,7 @@
         <v>76</v>
       </c>
       <c r="C2470">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2470">
         <v>41</v>
@@ -42992,7 +42985,7 @@
         <v>76</v>
       </c>
       <c r="C2471">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2471">
         <v>41</v>
@@ -43009,7 +43002,7 @@
         <v>76</v>
       </c>
       <c r="C2472">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2472">
         <v>41</v>
@@ -43026,7 +43019,7 @@
         <v>76</v>
       </c>
       <c r="C2473">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2473">
         <v>41</v>
@@ -43043,7 +43036,7 @@
         <v>76</v>
       </c>
       <c r="C2474">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2474">
         <v>41</v>
@@ -43060,7 +43053,7 @@
         <v>76</v>
       </c>
       <c r="C2475">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2475">
         <v>41</v>
@@ -43094,7 +43087,7 @@
         <v>77</v>
       </c>
       <c r="C2477">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2477">
         <v>41</v>
@@ -43111,7 +43104,7 @@
         <v>77</v>
       </c>
       <c r="C2478">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2478">
         <v>41</v>
@@ -43128,7 +43121,7 @@
         <v>77</v>
       </c>
       <c r="C2479">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2479">
         <v>41</v>
@@ -43145,7 +43138,7 @@
         <v>77</v>
       </c>
       <c r="C2480">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2480">
         <v>41</v>
@@ -43162,7 +43155,7 @@
         <v>77</v>
       </c>
       <c r="C2481">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2481">
         <v>41</v>
@@ -43179,7 +43172,7 @@
         <v>77</v>
       </c>
       <c r="C2482">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2482">
         <v>41</v>
@@ -43196,7 +43189,7 @@
         <v>77</v>
       </c>
       <c r="C2483">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2483">
         <v>41</v>
@@ -43213,7 +43206,7 @@
         <v>77</v>
       </c>
       <c r="C2484">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2484">
         <v>41</v>
@@ -43995,7 +43988,7 @@
         <v>82</v>
       </c>
       <c r="C2530">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2530">
         <v>41</v>
@@ -44012,7 +44005,7 @@
         <v>82</v>
       </c>
       <c r="C2531">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2531">
         <v>41</v>
@@ -44029,7 +44022,7 @@
         <v>82</v>
       </c>
       <c r="C2532">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2532">
         <v>41</v>
@@ -44046,7 +44039,7 @@
         <v>82</v>
       </c>
       <c r="C2533">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2533">
         <v>41</v>
@@ -44063,7 +44056,7 @@
         <v>82</v>
       </c>
       <c r="C2534">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2534">
         <v>41</v>
@@ -44080,7 +44073,7 @@
         <v>82</v>
       </c>
       <c r="C2535">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2535">
         <v>41</v>
@@ -44097,7 +44090,7 @@
         <v>82</v>
       </c>
       <c r="C2536">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2536">
         <v>41</v>
@@ -44114,7 +44107,7 @@
         <v>82</v>
       </c>
       <c r="C2537">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2537">
         <v>41</v>
@@ -44165,7 +44158,7 @@
         <v>83</v>
       </c>
       <c r="C2540">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2540">
         <v>41</v>
@@ -44182,7 +44175,7 @@
         <v>83</v>
       </c>
       <c r="C2541">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2541">
         <v>41</v>
@@ -44199,7 +44192,7 @@
         <v>83</v>
       </c>
       <c r="C2542">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2542">
         <v>41</v>
@@ -44216,7 +44209,7 @@
         <v>83</v>
       </c>
       <c r="C2543">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2543">
         <v>41</v>
@@ -44233,7 +44226,7 @@
         <v>83</v>
       </c>
       <c r="C2544">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2544">
         <v>41</v>
@@ -44250,7 +44243,7 @@
         <v>83</v>
       </c>
       <c r="C2545">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2545">
         <v>41</v>
@@ -44267,7 +44260,7 @@
         <v>83</v>
       </c>
       <c r="C2546">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2546">
         <v>41</v>
@@ -44284,7 +44277,7 @@
         <v>83</v>
       </c>
       <c r="C2547">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2547">
         <v>41</v>
@@ -44335,7 +44328,7 @@
         <v>84</v>
       </c>
       <c r="C2550">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2550">
         <v>41</v>
@@ -44352,7 +44345,7 @@
         <v>84</v>
       </c>
       <c r="C2551">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2551">
         <v>41</v>
@@ -44369,7 +44362,7 @@
         <v>84</v>
       </c>
       <c r="C2552">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2552">
         <v>41</v>
@@ -44386,7 +44379,7 @@
         <v>84</v>
       </c>
       <c r="C2553">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2553">
         <v>41</v>
@@ -44403,7 +44396,7 @@
         <v>84</v>
       </c>
       <c r="C2554">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2554">
         <v>41</v>
@@ -44420,7 +44413,7 @@
         <v>84</v>
       </c>
       <c r="C2555">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2555">
         <v>41</v>
@@ -44437,7 +44430,7 @@
         <v>84</v>
       </c>
       <c r="C2556">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2556">
         <v>41</v>
@@ -44454,7 +44447,7 @@
         <v>84</v>
       </c>
       <c r="C2557">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2557">
         <v>41</v>
@@ -44505,7 +44498,7 @@
         <v>85</v>
       </c>
       <c r="C2560">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2560">
         <v>41</v>
@@ -44522,7 +44515,7 @@
         <v>85</v>
       </c>
       <c r="C2561">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2561">
         <v>41</v>
@@ -44539,7 +44532,7 @@
         <v>85</v>
       </c>
       <c r="C2562">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2562">
         <v>41</v>
@@ -44556,7 +44549,7 @@
         <v>85</v>
       </c>
       <c r="C2563">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2563">
         <v>41</v>
@@ -44573,7 +44566,7 @@
         <v>85</v>
       </c>
       <c r="C2564">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2564">
         <v>41</v>
@@ -44590,7 +44583,7 @@
         <v>85</v>
       </c>
       <c r="C2565">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2565">
         <v>41</v>
@@ -44607,7 +44600,7 @@
         <v>85</v>
       </c>
       <c r="C2566">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2566">
         <v>41</v>
@@ -44624,7 +44617,7 @@
         <v>85</v>
       </c>
       <c r="C2567">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2567">
         <v>41</v>
@@ -44675,7 +44668,7 @@
         <v>86</v>
       </c>
       <c r="C2570">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2570">
         <v>41</v>
@@ -44692,7 +44685,7 @@
         <v>86</v>
       </c>
       <c r="C2571">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2571">
         <v>41</v>
@@ -44709,7 +44702,7 @@
         <v>86</v>
       </c>
       <c r="C2572">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2572">
         <v>41</v>
@@ -44726,7 +44719,7 @@
         <v>86</v>
       </c>
       <c r="C2573">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2573">
         <v>41</v>
@@ -44743,7 +44736,7 @@
         <v>86</v>
       </c>
       <c r="C2574">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2574">
         <v>41</v>
@@ -44760,7 +44753,7 @@
         <v>86</v>
       </c>
       <c r="C2575">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2575">
         <v>41</v>
@@ -44777,7 +44770,7 @@
         <v>86</v>
       </c>
       <c r="C2576">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2576">
         <v>41</v>
@@ -44794,7 +44787,7 @@
         <v>86</v>
       </c>
       <c r="C2577">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2577">
         <v>41</v>
@@ -54722,7 +54715,7 @@
         <v>2</v>
       </c>
       <c r="C3161">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3161">
         <v>13</v>
@@ -54739,7 +54732,7 @@
         <v>2</v>
       </c>
       <c r="C3162">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3162">
         <v>13</v>
@@ -54773,7 +54766,7 @@
         <v>2</v>
       </c>
       <c r="C3164">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3164">
         <v>13</v>
@@ -54790,7 +54783,7 @@
         <v>2</v>
       </c>
       <c r="C3165">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3165">
         <v>13</v>
@@ -54807,7 +54800,7 @@
         <v>3</v>
       </c>
       <c r="C3166">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3166">
         <v>13</v>
@@ -54824,7 +54817,7 @@
         <v>3</v>
       </c>
       <c r="C3167">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3167">
         <v>13</v>
@@ -54858,7 +54851,7 @@
         <v>3</v>
       </c>
       <c r="C3169">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3169">
         <v>13</v>
@@ -54875,7 +54868,7 @@
         <v>3</v>
       </c>
       <c r="C3170">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3170">
         <v>13</v>
@@ -54892,7 +54885,7 @@
         <v>4</v>
       </c>
       <c r="C3171">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3171">
         <v>13</v>
@@ -54909,7 +54902,7 @@
         <v>4</v>
       </c>
       <c r="C3172">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3172">
         <v>13</v>
@@ -54943,7 +54936,7 @@
         <v>4</v>
       </c>
       <c r="C3174">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3174">
         <v>13</v>
@@ -54960,7 +54953,7 @@
         <v>4</v>
       </c>
       <c r="C3175">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3175">
         <v>13</v>
@@ -54977,7 +54970,7 @@
         <v>5</v>
       </c>
       <c r="C3176">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3176">
         <v>13</v>
@@ -54994,7 +54987,7 @@
         <v>5</v>
       </c>
       <c r="C3177">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3177">
         <v>13</v>
@@ -55028,7 +55021,7 @@
         <v>5</v>
       </c>
       <c r="C3179">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3179">
         <v>13</v>
@@ -55045,7 +55038,7 @@
         <v>5</v>
       </c>
       <c r="C3180">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3180">
         <v>13</v>
@@ -55062,7 +55055,7 @@
         <v>6</v>
       </c>
       <c r="C3181">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3181">
         <v>13</v>
@@ -55079,7 +55072,7 @@
         <v>6</v>
       </c>
       <c r="C3182">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3182">
         <v>13</v>
@@ -55113,7 +55106,7 @@
         <v>6</v>
       </c>
       <c r="C3184">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3184">
         <v>13</v>
@@ -55130,7 +55123,7 @@
         <v>6</v>
       </c>
       <c r="C3185">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3185">
         <v>13</v>
@@ -55147,7 +55140,7 @@
         <v>7</v>
       </c>
       <c r="C3186">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3186">
         <v>13</v>
@@ -55164,7 +55157,7 @@
         <v>7</v>
       </c>
       <c r="C3187">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3187">
         <v>13</v>
@@ -55198,7 +55191,7 @@
         <v>7</v>
       </c>
       <c r="C3189">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3189">
         <v>13</v>
@@ -55215,7 +55208,7 @@
         <v>7</v>
       </c>
       <c r="C3190">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3190">
         <v>13</v>
@@ -55232,7 +55225,7 @@
         <v>8</v>
       </c>
       <c r="C3191">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3191">
         <v>13</v>
@@ -55249,7 +55242,7 @@
         <v>8</v>
       </c>
       <c r="C3192">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3192">
         <v>13</v>
@@ -55283,7 +55276,7 @@
         <v>8</v>
       </c>
       <c r="C3194">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3194">
         <v>13</v>
@@ -55300,7 +55293,7 @@
         <v>8</v>
       </c>
       <c r="C3195">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3195">
         <v>13</v>
@@ -55317,7 +55310,7 @@
         <v>9</v>
       </c>
       <c r="C3196">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3196">
         <v>13</v>
@@ -55334,7 +55327,7 @@
         <v>9</v>
       </c>
       <c r="C3197">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3197">
         <v>13</v>
@@ -55368,7 +55361,7 @@
         <v>9</v>
       </c>
       <c r="C3199">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3199">
         <v>13</v>
@@ -55385,7 +55378,7 @@
         <v>9</v>
       </c>
       <c r="C3200">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3200">
         <v>13</v>
@@ -55402,7 +55395,7 @@
         <v>10</v>
       </c>
       <c r="C3201">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3201">
         <v>13</v>
@@ -55436,7 +55429,7 @@
         <v>10</v>
       </c>
       <c r="C3203">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3203">
         <v>13</v>
@@ -55504,7 +55497,7 @@
         <v>15</v>
       </c>
       <c r="C3207">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3207">
         <v>13</v>
@@ -55521,7 +55514,7 @@
         <v>15</v>
       </c>
       <c r="C3208">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3208">
         <v>13</v>
@@ -55555,7 +55548,7 @@
         <v>15</v>
       </c>
       <c r="C3210">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3210">
         <v>13</v>
@@ -55572,7 +55565,7 @@
         <v>15</v>
       </c>
       <c r="C3211">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3211">
         <v>13</v>
@@ -55589,7 +55582,7 @@
         <v>16</v>
       </c>
       <c r="C3212">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3212">
         <v>13</v>
@@ -55606,7 +55599,7 @@
         <v>16</v>
       </c>
       <c r="C3213">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3213">
         <v>13</v>
@@ -55640,7 +55633,7 @@
         <v>16</v>
       </c>
       <c r="C3215">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3215">
         <v>13</v>
@@ -55657,7 +55650,7 @@
         <v>16</v>
       </c>
       <c r="C3216">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3216">
         <v>13</v>
@@ -55674,7 +55667,7 @@
         <v>17</v>
       </c>
       <c r="C3217">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3217">
         <v>13</v>
@@ -55691,7 +55684,7 @@
         <v>17</v>
       </c>
       <c r="C3218">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3218">
         <v>13</v>
@@ -55725,7 +55718,7 @@
         <v>17</v>
       </c>
       <c r="C3220">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3220">
         <v>13</v>
@@ -55742,7 +55735,7 @@
         <v>17</v>
       </c>
       <c r="C3221">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3221">
         <v>13</v>
@@ -55759,7 +55752,7 @@
         <v>18</v>
       </c>
       <c r="C3222">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3222">
         <v>13</v>
@@ -55776,7 +55769,7 @@
         <v>18</v>
       </c>
       <c r="C3223">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3223">
         <v>13</v>
@@ -55810,7 +55803,7 @@
         <v>18</v>
       </c>
       <c r="C3225">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3225">
         <v>13</v>
@@ -55827,7 +55820,7 @@
         <v>18</v>
       </c>
       <c r="C3226">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3226">
         <v>13</v>
@@ -55844,7 +55837,7 @@
         <v>19</v>
       </c>
       <c r="C3227">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3227">
         <v>13</v>
@@ -55861,7 +55854,7 @@
         <v>19</v>
       </c>
       <c r="C3228">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3228">
         <v>13</v>
@@ -55895,7 +55888,7 @@
         <v>19</v>
       </c>
       <c r="C3230">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3230">
         <v>13</v>
@@ -55912,7 +55905,7 @@
         <v>19</v>
       </c>
       <c r="C3231">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3231">
         <v>13</v>
@@ -55929,7 +55922,7 @@
         <v>20</v>
       </c>
       <c r="C3232">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3232">
         <v>13</v>
@@ -55946,7 +55939,7 @@
         <v>20</v>
       </c>
       <c r="C3233">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3233">
         <v>13</v>
@@ -55980,7 +55973,7 @@
         <v>20</v>
       </c>
       <c r="C3235">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3235">
         <v>13</v>
@@ -55997,7 +55990,7 @@
         <v>20</v>
       </c>
       <c r="C3236">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3236">
         <v>13</v>
@@ -56014,7 +56007,7 @@
         <v>21</v>
       </c>
       <c r="C3237">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3237">
         <v>13</v>
@@ -56031,7 +56024,7 @@
         <v>21</v>
       </c>
       <c r="C3238">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3238">
         <v>13</v>
@@ -56065,7 +56058,7 @@
         <v>21</v>
       </c>
       <c r="C3240">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3240">
         <v>13</v>
@@ -56082,7 +56075,7 @@
         <v>21</v>
       </c>
       <c r="C3241">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3241">
         <v>13</v>
@@ -56099,7 +56092,7 @@
         <v>22</v>
       </c>
       <c r="C3242">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3242">
         <v>13</v>
@@ -56116,7 +56109,7 @@
         <v>22</v>
       </c>
       <c r="C3243">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3243">
         <v>13</v>
@@ -56150,7 +56143,7 @@
         <v>22</v>
       </c>
       <c r="C3245">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3245">
         <v>13</v>
@@ -56167,7 +56160,7 @@
         <v>22</v>
       </c>
       <c r="C3246">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3246">
         <v>13</v>
@@ -56184,7 +56177,7 @@
         <v>23</v>
       </c>
       <c r="C3247">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3247">
         <v>13</v>
@@ -56201,7 +56194,7 @@
         <v>23</v>
       </c>
       <c r="C3248">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3248">
         <v>13</v>
@@ -56235,7 +56228,7 @@
         <v>23</v>
       </c>
       <c r="C3250">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3250">
         <v>13</v>
@@ -56252,7 +56245,7 @@
         <v>23</v>
       </c>
       <c r="C3251">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3251">
         <v>13</v>
@@ -56269,7 +56262,7 @@
         <v>24</v>
       </c>
       <c r="C3252">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3252">
         <v>13</v>
@@ -56286,7 +56279,7 @@
         <v>24</v>
       </c>
       <c r="C3253">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3253">
         <v>13</v>
@@ -56320,7 +56313,7 @@
         <v>24</v>
       </c>
       <c r="C3255">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3255">
         <v>13</v>
@@ -56337,7 +56330,7 @@
         <v>24</v>
       </c>
       <c r="C3256">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3256">
         <v>13</v>
@@ -56354,7 +56347,7 @@
         <v>25</v>
       </c>
       <c r="C3257">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3257">
         <v>13</v>
@@ -56371,7 +56364,7 @@
         <v>25</v>
       </c>
       <c r="C3258">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3258">
         <v>13</v>
@@ -56405,7 +56398,7 @@
         <v>25</v>
       </c>
       <c r="C3260">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3260">
         <v>13</v>
@@ -56422,7 +56415,7 @@
         <v>25</v>
       </c>
       <c r="C3261">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3261">
         <v>13</v>
@@ -56439,7 +56432,7 @@
         <v>26</v>
       </c>
       <c r="C3262">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3262">
         <v>13</v>
@@ -56456,7 +56449,7 @@
         <v>26</v>
       </c>
       <c r="C3263">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3263">
         <v>13</v>
@@ -56490,7 +56483,7 @@
         <v>26</v>
       </c>
       <c r="C3265">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3265">
         <v>13</v>
@@ -56507,7 +56500,7 @@
         <v>26</v>
       </c>
       <c r="C3266">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3266">
         <v>13</v>
@@ -56524,7 +56517,7 @@
         <v>27</v>
       </c>
       <c r="C3267">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3267">
         <v>13</v>
@@ -56541,7 +56534,7 @@
         <v>27</v>
       </c>
       <c r="C3268">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3268">
         <v>13</v>
@@ -56575,7 +56568,7 @@
         <v>27</v>
       </c>
       <c r="C3270">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3270">
         <v>13</v>
@@ -56592,7 +56585,7 @@
         <v>27</v>
       </c>
       <c r="C3271">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3271">
         <v>13</v>
@@ -56609,7 +56602,7 @@
         <v>28</v>
       </c>
       <c r="C3272">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3272">
         <v>13</v>
@@ -56626,7 +56619,7 @@
         <v>28</v>
       </c>
       <c r="C3273">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3273">
         <v>13</v>
@@ -56660,7 +56653,7 @@
         <v>28</v>
       </c>
       <c r="C3275">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3275">
         <v>13</v>
@@ -56677,7 +56670,7 @@
         <v>28</v>
       </c>
       <c r="C3276">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3276">
         <v>13</v>
@@ -56694,7 +56687,7 @@
         <v>29</v>
       </c>
       <c r="C3277">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3277">
         <v>13</v>
@@ -56711,7 +56704,7 @@
         <v>29</v>
       </c>
       <c r="C3278">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3278">
         <v>13</v>
@@ -56745,7 +56738,7 @@
         <v>29</v>
       </c>
       <c r="C3280">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3280">
         <v>13</v>
@@ -56762,7 +56755,7 @@
         <v>29</v>
       </c>
       <c r="C3281">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3281">
         <v>13</v>
@@ -56779,7 +56772,7 @@
         <v>30</v>
       </c>
       <c r="C3282">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3282">
         <v>13</v>
@@ -56796,7 +56789,7 @@
         <v>30</v>
       </c>
       <c r="C3283">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3283">
         <v>13</v>
@@ -56830,7 +56823,7 @@
         <v>30</v>
       </c>
       <c r="C3285">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3285">
         <v>13</v>
@@ -56847,7 +56840,7 @@
         <v>30</v>
       </c>
       <c r="C3286">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3286">
         <v>13</v>
@@ -56864,7 +56857,7 @@
         <v>31</v>
       </c>
       <c r="C3287">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3287">
         <v>13</v>
@@ -56881,7 +56874,7 @@
         <v>31</v>
       </c>
       <c r="C3288">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3288">
         <v>13</v>
@@ -56915,7 +56908,7 @@
         <v>31</v>
       </c>
       <c r="C3290">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3290">
         <v>13</v>
@@ -56932,7 +56925,7 @@
         <v>31</v>
       </c>
       <c r="C3291">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3291">
         <v>13</v>
@@ -56949,7 +56942,7 @@
         <v>32</v>
       </c>
       <c r="C3292">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3292">
         <v>13</v>
@@ -56966,7 +56959,7 @@
         <v>32</v>
       </c>
       <c r="C3293">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3293">
         <v>13</v>
@@ -57000,7 +56993,7 @@
         <v>32</v>
       </c>
       <c r="C3295">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3295">
         <v>13</v>
@@ -57017,7 +57010,7 @@
         <v>32</v>
       </c>
       <c r="C3296">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3296">
         <v>13</v>
@@ -57034,7 +57027,7 @@
         <v>33</v>
       </c>
       <c r="C3297">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3297">
         <v>13</v>
@@ -57051,7 +57044,7 @@
         <v>33</v>
       </c>
       <c r="C3298">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3298">
         <v>13</v>
@@ -57085,7 +57078,7 @@
         <v>33</v>
       </c>
       <c r="C3300">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3300">
         <v>13</v>
@@ -57102,7 +57095,7 @@
         <v>33</v>
       </c>
       <c r="C3301">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3301">
         <v>13</v>
@@ -57119,7 +57112,7 @@
         <v>34</v>
       </c>
       <c r="C3302">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3302">
         <v>13</v>
@@ -57136,7 +57129,7 @@
         <v>34</v>
       </c>
       <c r="C3303">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3303">
         <v>13</v>
@@ -57170,7 +57163,7 @@
         <v>34</v>
       </c>
       <c r="C3305">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3305">
         <v>13</v>
@@ -57187,7 +57180,7 @@
         <v>34</v>
       </c>
       <c r="C3306">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3306">
         <v>13</v>
@@ -57204,7 +57197,7 @@
         <v>35</v>
       </c>
       <c r="C3307">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3307">
         <v>13</v>
@@ -57221,7 +57214,7 @@
         <v>35</v>
       </c>
       <c r="C3308">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3308">
         <v>13</v>
@@ -57255,7 +57248,7 @@
         <v>35</v>
       </c>
       <c r="C3310">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3310">
         <v>13</v>
@@ -57272,7 +57265,7 @@
         <v>35</v>
       </c>
       <c r="C3311">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3311">
         <v>13</v>
@@ -57289,7 +57282,7 @@
         <v>36</v>
       </c>
       <c r="C3312">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3312">
         <v>13</v>
@@ -57306,7 +57299,7 @@
         <v>36</v>
       </c>
       <c r="C3313">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3313">
         <v>13</v>
@@ -57340,7 +57333,7 @@
         <v>36</v>
       </c>
       <c r="C3315">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3315">
         <v>13</v>
@@ -57357,7 +57350,7 @@
         <v>36</v>
       </c>
       <c r="C3316">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3316">
         <v>13</v>
@@ -57374,7 +57367,7 @@
         <v>37</v>
       </c>
       <c r="C3317">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3317">
         <v>13</v>
@@ -57391,7 +57384,7 @@
         <v>37</v>
       </c>
       <c r="C3318">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3318">
         <v>13</v>
@@ -57425,7 +57418,7 @@
         <v>37</v>
       </c>
       <c r="C3320">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3320">
         <v>13</v>
@@ -57442,7 +57435,7 @@
         <v>37</v>
       </c>
       <c r="C3321">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3321">
         <v>13</v>
@@ -57459,7 +57452,7 @@
         <v>38</v>
       </c>
       <c r="C3322">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3322">
         <v>13</v>
@@ -57493,7 +57486,7 @@
         <v>38</v>
       </c>
       <c r="C3324">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3324">
         <v>13</v>
@@ -57561,7 +57554,7 @@
         <v>43</v>
       </c>
       <c r="C3328">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3328">
         <v>41</v>
@@ -57578,7 +57571,7 @@
         <v>43</v>
       </c>
       <c r="C3329">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3329">
         <v>41</v>
@@ -57612,7 +57605,7 @@
         <v>43</v>
       </c>
       <c r="C3331">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3331">
         <v>41</v>
@@ -57629,7 +57622,7 @@
         <v>43</v>
       </c>
       <c r="C3332">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3332">
         <v>41</v>
@@ -57646,7 +57639,7 @@
         <v>44</v>
       </c>
       <c r="C3333">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3333">
         <v>41</v>
@@ -57663,7 +57656,7 @@
         <v>44</v>
       </c>
       <c r="C3334">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3334">
         <v>41</v>
@@ -57697,7 +57690,7 @@
         <v>44</v>
       </c>
       <c r="C3336">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3336">
         <v>41</v>
@@ -57714,7 +57707,7 @@
         <v>44</v>
       </c>
       <c r="C3337">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3337">
         <v>41</v>
@@ -57731,7 +57724,7 @@
         <v>45</v>
       </c>
       <c r="C3338">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3338">
         <v>41</v>
@@ -57748,7 +57741,7 @@
         <v>45</v>
       </c>
       <c r="C3339">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3339">
         <v>41</v>
@@ -57782,7 +57775,7 @@
         <v>45</v>
       </c>
       <c r="C3341">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3341">
         <v>41</v>
@@ -57799,7 +57792,7 @@
         <v>45</v>
       </c>
       <c r="C3342">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3342">
         <v>41</v>
@@ -57816,7 +57809,7 @@
         <v>46</v>
       </c>
       <c r="C3343">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3343">
         <v>41</v>
@@ -57833,7 +57826,7 @@
         <v>46</v>
       </c>
       <c r="C3344">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3344">
         <v>41</v>
@@ -57867,7 +57860,7 @@
         <v>46</v>
       </c>
       <c r="C3346">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3346">
         <v>41</v>
@@ -57884,7 +57877,7 @@
         <v>46</v>
       </c>
       <c r="C3347">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3347">
         <v>41</v>
@@ -57901,7 +57894,7 @@
         <v>47</v>
       </c>
       <c r="C3348">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3348">
         <v>41</v>
@@ -57918,7 +57911,7 @@
         <v>47</v>
       </c>
       <c r="C3349">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3349">
         <v>41</v>
@@ -57952,7 +57945,7 @@
         <v>47</v>
       </c>
       <c r="C3351">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3351">
         <v>41</v>
@@ -57969,7 +57962,7 @@
         <v>47</v>
       </c>
       <c r="C3352">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3352">
         <v>41</v>
@@ -57986,7 +57979,7 @@
         <v>48</v>
       </c>
       <c r="C3353">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3353">
         <v>41</v>
@@ -58003,7 +57996,7 @@
         <v>48</v>
       </c>
       <c r="C3354">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3354">
         <v>41</v>
@@ -58037,7 +58030,7 @@
         <v>48</v>
       </c>
       <c r="C3356">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3356">
         <v>41</v>
@@ -58054,7 +58047,7 @@
         <v>48</v>
       </c>
       <c r="C3357">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3357">
         <v>41</v>
@@ -58071,7 +58064,7 @@
         <v>49</v>
       </c>
       <c r="C3358">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3358">
         <v>41</v>
@@ -58088,7 +58081,7 @@
         <v>49</v>
       </c>
       <c r="C3359">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3359">
         <v>41</v>
@@ -58122,7 +58115,7 @@
         <v>49</v>
       </c>
       <c r="C3361">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3361">
         <v>41</v>
@@ -58139,7 +58132,7 @@
         <v>49</v>
       </c>
       <c r="C3362">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3362">
         <v>41</v>
@@ -58156,7 +58149,7 @@
         <v>50</v>
       </c>
       <c r="C3363">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3363">
         <v>41</v>
@@ -58173,7 +58166,7 @@
         <v>50</v>
       </c>
       <c r="C3364">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3364">
         <v>41</v>
@@ -58207,7 +58200,7 @@
         <v>50</v>
       </c>
       <c r="C3366">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3366">
         <v>41</v>
@@ -58224,7 +58217,7 @@
         <v>50</v>
       </c>
       <c r="C3367">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3367">
         <v>41</v>
@@ -58241,7 +58234,7 @@
         <v>51</v>
       </c>
       <c r="C3368">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3368">
         <v>41</v>
@@ -58258,7 +58251,7 @@
         <v>51</v>
       </c>
       <c r="C3369">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3369">
         <v>41</v>
@@ -58292,7 +58285,7 @@
         <v>51</v>
       </c>
       <c r="C3371">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3371">
         <v>41</v>
@@ -58309,7 +58302,7 @@
         <v>51</v>
       </c>
       <c r="C3372">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3372">
         <v>41</v>
@@ -58326,7 +58319,7 @@
         <v>52</v>
       </c>
       <c r="C3373">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3373">
         <v>41</v>
@@ -58343,7 +58336,7 @@
         <v>52</v>
       </c>
       <c r="C3374">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3374">
         <v>41</v>
@@ -58377,7 +58370,7 @@
         <v>52</v>
       </c>
       <c r="C3376">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3376">
         <v>41</v>
@@ -58394,7 +58387,7 @@
         <v>52</v>
       </c>
       <c r="C3377">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3377">
         <v>41</v>
@@ -58411,7 +58404,7 @@
         <v>53</v>
       </c>
       <c r="C3378">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3378">
         <v>41</v>
@@ -58428,7 +58421,7 @@
         <v>53</v>
       </c>
       <c r="C3379">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3379">
         <v>41</v>
@@ -58462,7 +58455,7 @@
         <v>53</v>
       </c>
       <c r="C3381">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3381">
         <v>41</v>
@@ -58479,7 +58472,7 @@
         <v>53</v>
       </c>
       <c r="C3382">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3382">
         <v>41</v>
@@ -58496,7 +58489,7 @@
         <v>54</v>
       </c>
       <c r="C3383">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3383">
         <v>41</v>
@@ -58513,7 +58506,7 @@
         <v>54</v>
       </c>
       <c r="C3384">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3384">
         <v>41</v>
@@ -58547,7 +58540,7 @@
         <v>54</v>
       </c>
       <c r="C3386">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3386">
         <v>41</v>
@@ -58564,7 +58557,7 @@
         <v>54</v>
       </c>
       <c r="C3387">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3387">
         <v>41</v>
@@ -58581,7 +58574,7 @@
         <v>55</v>
       </c>
       <c r="C3388">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3388">
         <v>41</v>
@@ -58598,7 +58591,7 @@
         <v>55</v>
       </c>
       <c r="C3389">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3389">
         <v>41</v>
@@ -58632,7 +58625,7 @@
         <v>55</v>
       </c>
       <c r="C3391">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3391">
         <v>41</v>
@@ -58649,7 +58642,7 @@
         <v>55</v>
       </c>
       <c r="C3392">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3392">
         <v>41</v>
@@ -58666,7 +58659,7 @@
         <v>56</v>
       </c>
       <c r="C3393">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3393">
         <v>41</v>
@@ -58683,7 +58676,7 @@
         <v>56</v>
       </c>
       <c r="C3394">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3394">
         <v>41</v>
@@ -58717,7 +58710,7 @@
         <v>56</v>
       </c>
       <c r="C3396">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3396">
         <v>41</v>
@@ -58734,7 +58727,7 @@
         <v>56</v>
       </c>
       <c r="C3397">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3397">
         <v>41</v>
@@ -58751,7 +58744,7 @@
         <v>57</v>
       </c>
       <c r="C3398">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3398">
         <v>41</v>
@@ -58768,7 +58761,7 @@
         <v>57</v>
       </c>
       <c r="C3399">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3399">
         <v>41</v>
@@ -58802,7 +58795,7 @@
         <v>57</v>
       </c>
       <c r="C3401">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3401">
         <v>41</v>
@@ -58819,7 +58812,7 @@
         <v>57</v>
       </c>
       <c r="C3402">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3402">
         <v>41</v>
@@ -58836,7 +58829,7 @@
         <v>58</v>
       </c>
       <c r="C3403">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3403">
         <v>41</v>
@@ -58853,7 +58846,7 @@
         <v>58</v>
       </c>
       <c r="C3404">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3404">
         <v>41</v>
@@ -58887,7 +58880,7 @@
         <v>58</v>
       </c>
       <c r="C3406">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3406">
         <v>41</v>
@@ -58904,7 +58897,7 @@
         <v>58</v>
       </c>
       <c r="C3407">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3407">
         <v>41</v>
@@ -58921,7 +58914,7 @@
         <v>59</v>
       </c>
       <c r="C3408">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3408">
         <v>41</v>
@@ -58938,7 +58931,7 @@
         <v>59</v>
       </c>
       <c r="C3409">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3409">
         <v>41</v>
@@ -58972,7 +58965,7 @@
         <v>59</v>
       </c>
       <c r="C3411">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3411">
         <v>41</v>
@@ -58989,7 +58982,7 @@
         <v>59</v>
       </c>
       <c r="C3412">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3412">
         <v>41</v>
@@ -59006,7 +58999,7 @@
         <v>60</v>
       </c>
       <c r="C3413">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3413">
         <v>41</v>
@@ -59023,7 +59016,7 @@
         <v>60</v>
       </c>
       <c r="C3414">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3414">
         <v>41</v>
@@ -59057,7 +59050,7 @@
         <v>60</v>
       </c>
       <c r="C3416">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3416">
         <v>41</v>
@@ -59074,7 +59067,7 @@
         <v>60</v>
       </c>
       <c r="C3417">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3417">
         <v>41</v>
@@ -59091,7 +59084,7 @@
         <v>61</v>
       </c>
       <c r="C3418">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3418">
         <v>41</v>
@@ -59108,7 +59101,7 @@
         <v>61</v>
       </c>
       <c r="C3419">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3419">
         <v>41</v>
@@ -59142,7 +59135,7 @@
         <v>61</v>
       </c>
       <c r="C3421">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3421">
         <v>41</v>
@@ -59159,7 +59152,7 @@
         <v>61</v>
       </c>
       <c r="C3422">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3422">
         <v>41</v>
@@ -59176,7 +59169,7 @@
         <v>62</v>
       </c>
       <c r="C3423">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3423">
         <v>41</v>
@@ -59193,7 +59186,7 @@
         <v>62</v>
       </c>
       <c r="C3424">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3424">
         <v>41</v>
@@ -59227,7 +59220,7 @@
         <v>62</v>
       </c>
       <c r="C3426">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3426">
         <v>41</v>
@@ -59244,7 +59237,7 @@
         <v>62</v>
       </c>
       <c r="C3427">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3427">
         <v>41</v>
@@ -59261,7 +59254,7 @@
         <v>63</v>
       </c>
       <c r="C3428">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3428">
         <v>41</v>
@@ -59278,7 +59271,7 @@
         <v>63</v>
       </c>
       <c r="C3429">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3429">
         <v>41</v>
@@ -59312,7 +59305,7 @@
         <v>63</v>
       </c>
       <c r="C3431">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3431">
         <v>41</v>
@@ -59329,7 +59322,7 @@
         <v>63</v>
       </c>
       <c r="C3432">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3432">
         <v>41</v>
@@ -59346,7 +59339,7 @@
         <v>64</v>
       </c>
       <c r="C3433">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3433">
         <v>41</v>
@@ -59363,7 +59356,7 @@
         <v>64</v>
       </c>
       <c r="C3434">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3434">
         <v>41</v>
@@ -59397,7 +59390,7 @@
         <v>64</v>
       </c>
       <c r="C3436">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3436">
         <v>41</v>
@@ -59414,7 +59407,7 @@
         <v>64</v>
       </c>
       <c r="C3437">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3437">
         <v>41</v>
@@ -59431,7 +59424,7 @@
         <v>65</v>
       </c>
       <c r="C3438">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3438">
         <v>41</v>
@@ -59448,7 +59441,7 @@
         <v>65</v>
       </c>
       <c r="C3439">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3439">
         <v>41</v>
@@ -59482,7 +59475,7 @@
         <v>65</v>
       </c>
       <c r="C3441">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3441">
         <v>41</v>
@@ -59499,7 +59492,7 @@
         <v>65</v>
       </c>
       <c r="C3442">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3442">
         <v>41</v>
@@ -59516,7 +59509,7 @@
         <v>66</v>
       </c>
       <c r="C3443">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3443">
         <v>41</v>
@@ -59533,7 +59526,7 @@
         <v>66</v>
       </c>
       <c r="C3444">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3444">
         <v>41</v>
@@ -59567,7 +59560,7 @@
         <v>66</v>
       </c>
       <c r="C3446">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3446">
         <v>41</v>
@@ -59584,7 +59577,7 @@
         <v>66</v>
       </c>
       <c r="C3447">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3447">
         <v>41</v>
@@ -59601,7 +59594,7 @@
         <v>67</v>
       </c>
       <c r="C3448">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3448">
         <v>41</v>
@@ -59618,7 +59611,7 @@
         <v>67</v>
       </c>
       <c r="C3449">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3449">
         <v>41</v>
@@ -59652,7 +59645,7 @@
         <v>67</v>
       </c>
       <c r="C3451">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3451">
         <v>41</v>
@@ -59669,7 +59662,7 @@
         <v>67</v>
       </c>
       <c r="C3452">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3452">
         <v>41</v>
@@ -59686,7 +59679,7 @@
         <v>68</v>
       </c>
       <c r="C3453">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3453">
         <v>41</v>
@@ -59703,7 +59696,7 @@
         <v>68</v>
       </c>
       <c r="C3454">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3454">
         <v>41</v>
@@ -59737,7 +59730,7 @@
         <v>68</v>
       </c>
       <c r="C3456">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3456">
         <v>41</v>
@@ -59754,7 +59747,7 @@
         <v>68</v>
       </c>
       <c r="C3457">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3457">
         <v>41</v>
@@ -59771,7 +59764,7 @@
         <v>69</v>
       </c>
       <c r="C3458">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3458">
         <v>41</v>
@@ -59788,7 +59781,7 @@
         <v>69</v>
       </c>
       <c r="C3459">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3459">
         <v>41</v>
@@ -59822,7 +59815,7 @@
         <v>69</v>
       </c>
       <c r="C3461">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3461">
         <v>41</v>
@@ -59839,7 +59832,7 @@
         <v>69</v>
       </c>
       <c r="C3462">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3462">
         <v>41</v>
@@ -59856,7 +59849,7 @@
         <v>70</v>
       </c>
       <c r="C3463">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3463">
         <v>41</v>
@@ -59873,7 +59866,7 @@
         <v>70</v>
       </c>
       <c r="C3464">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3464">
         <v>41</v>
@@ -59907,7 +59900,7 @@
         <v>70</v>
       </c>
       <c r="C3466">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3466">
         <v>41</v>
@@ -59924,7 +59917,7 @@
         <v>70</v>
       </c>
       <c r="C3467">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3467">
         <v>41</v>
@@ -59941,7 +59934,7 @@
         <v>71</v>
       </c>
       <c r="C3468">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3468">
         <v>41</v>
@@ -59958,7 +59951,7 @@
         <v>71</v>
       </c>
       <c r="C3469">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3469">
         <v>41</v>
@@ -59992,7 +59985,7 @@
         <v>71</v>
       </c>
       <c r="C3471">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3471">
         <v>41</v>
@@ -60009,7 +60002,7 @@
         <v>71</v>
       </c>
       <c r="C3472">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3472">
         <v>41</v>
@@ -60026,7 +60019,7 @@
         <v>72</v>
       </c>
       <c r="C3473">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3473">
         <v>41</v>
@@ -60043,7 +60036,7 @@
         <v>72</v>
       </c>
       <c r="C3474">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3474">
         <v>41</v>
@@ -60077,7 +60070,7 @@
         <v>72</v>
       </c>
       <c r="C3476">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3476">
         <v>41</v>
@@ -60094,7 +60087,7 @@
         <v>72</v>
       </c>
       <c r="C3477">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3477">
         <v>41</v>
@@ -60111,7 +60104,7 @@
         <v>73</v>
       </c>
       <c r="C3478">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3478">
         <v>41</v>
@@ -60128,7 +60121,7 @@
         <v>73</v>
       </c>
       <c r="C3479">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3479">
         <v>41</v>
@@ -60162,7 +60155,7 @@
         <v>73</v>
       </c>
       <c r="C3481">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3481">
         <v>41</v>
@@ -60179,7 +60172,7 @@
         <v>73</v>
       </c>
       <c r="C3482">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3482">
         <v>41</v>
@@ -60196,7 +60189,7 @@
         <v>74</v>
       </c>
       <c r="C3483">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3483">
         <v>41</v>
@@ -60213,7 +60206,7 @@
         <v>74</v>
       </c>
       <c r="C3484">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3484">
         <v>41</v>
@@ -60247,7 +60240,7 @@
         <v>74</v>
       </c>
       <c r="C3486">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3486">
         <v>41</v>
@@ -60264,7 +60257,7 @@
         <v>74</v>
       </c>
       <c r="C3487">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3487">
         <v>41</v>
@@ -60281,7 +60274,7 @@
         <v>75</v>
       </c>
       <c r="C3488">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3488">
         <v>41</v>
@@ -60298,7 +60291,7 @@
         <v>75</v>
       </c>
       <c r="C3489">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3489">
         <v>41</v>
@@ -60332,7 +60325,7 @@
         <v>75</v>
       </c>
       <c r="C3491">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3491">
         <v>41</v>
@@ -60349,7 +60342,7 @@
         <v>75</v>
       </c>
       <c r="C3492">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3492">
         <v>41</v>
@@ -60366,7 +60359,7 @@
         <v>76</v>
       </c>
       <c r="C3493">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3493">
         <v>41</v>
@@ -60383,7 +60376,7 @@
         <v>76</v>
       </c>
       <c r="C3494">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3494">
         <v>41</v>
@@ -60417,7 +60410,7 @@
         <v>76</v>
       </c>
       <c r="C3496">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3496">
         <v>41</v>
@@ -60434,7 +60427,7 @@
         <v>76</v>
       </c>
       <c r="C3497">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3497">
         <v>41</v>
@@ -60451,7 +60444,7 @@
         <v>77</v>
       </c>
       <c r="C3498">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3498">
         <v>41</v>
@@ -60468,7 +60461,7 @@
         <v>77</v>
       </c>
       <c r="C3499">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3499">
         <v>41</v>
@@ -60502,7 +60495,7 @@
         <v>77</v>
       </c>
       <c r="C3501">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3501">
         <v>41</v>
@@ -60519,7 +60512,7 @@
         <v>77</v>
       </c>
       <c r="C3502">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3502">
         <v>41</v>
@@ -60536,7 +60529,7 @@
         <v>78</v>
       </c>
       <c r="C3503">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3503">
         <v>41</v>
@@ -60553,7 +60546,7 @@
         <v>78</v>
       </c>
       <c r="C3504">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3504">
         <v>41</v>
@@ -60587,7 +60580,7 @@
         <v>78</v>
       </c>
       <c r="C3506">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3506">
         <v>41</v>
@@ -60604,7 +60597,7 @@
         <v>78</v>
       </c>
       <c r="C3507">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3507">
         <v>41</v>
@@ -60621,7 +60614,7 @@
         <v>79</v>
       </c>
       <c r="C3508">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3508">
         <v>41</v>
@@ -60638,7 +60631,7 @@
         <v>79</v>
       </c>
       <c r="C3509">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3509">
         <v>41</v>
@@ -60672,7 +60665,7 @@
         <v>79</v>
       </c>
       <c r="C3511">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3511">
         <v>41</v>
@@ -60689,7 +60682,7 @@
         <v>79</v>
       </c>
       <c r="C3512">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3512">
         <v>41</v>
@@ -60706,7 +60699,7 @@
         <v>80</v>
       </c>
       <c r="C3513">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3513">
         <v>41</v>
@@ -60723,7 +60716,7 @@
         <v>80</v>
       </c>
       <c r="C3514">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3514">
         <v>41</v>
@@ -60757,7 +60750,7 @@
         <v>80</v>
       </c>
       <c r="C3516">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3516">
         <v>41</v>
@@ -60774,7 +60767,7 @@
         <v>80</v>
       </c>
       <c r="C3517">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3517">
         <v>41</v>
@@ -60791,7 +60784,7 @@
         <v>81</v>
       </c>
       <c r="C3518">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3518">
         <v>41</v>
@@ -60808,7 +60801,7 @@
         <v>81</v>
       </c>
       <c r="C3519">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3519">
         <v>41</v>
@@ -60842,7 +60835,7 @@
         <v>81</v>
       </c>
       <c r="C3521">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3521">
         <v>41</v>
@@ -60859,7 +60852,7 @@
         <v>81</v>
       </c>
       <c r="C3522">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3522">
         <v>41</v>
@@ -60876,7 +60869,7 @@
         <v>82</v>
       </c>
       <c r="C3523">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3523">
         <v>41</v>
@@ -60893,7 +60886,7 @@
         <v>82</v>
       </c>
       <c r="C3524">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3524">
         <v>41</v>
@@ -60927,7 +60920,7 @@
         <v>82</v>
       </c>
       <c r="C3526">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3526">
         <v>41</v>
@@ -60944,7 +60937,7 @@
         <v>82</v>
       </c>
       <c r="C3527">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3527">
         <v>41</v>
@@ -60961,7 +60954,7 @@
         <v>83</v>
       </c>
       <c r="C3528">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3528">
         <v>41</v>
@@ -60978,7 +60971,7 @@
         <v>83</v>
       </c>
       <c r="C3529">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3529">
         <v>41</v>
@@ -61012,7 +61005,7 @@
         <v>83</v>
       </c>
       <c r="C3531">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3531">
         <v>41</v>
@@ -61029,7 +61022,7 @@
         <v>83</v>
       </c>
       <c r="C3532">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3532">
         <v>41</v>
@@ -61046,7 +61039,7 @@
         <v>84</v>
       </c>
       <c r="C3533">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3533">
         <v>41</v>
@@ -61063,7 +61056,7 @@
         <v>84</v>
       </c>
       <c r="C3534">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3534">
         <v>41</v>
@@ -61097,7 +61090,7 @@
         <v>84</v>
       </c>
       <c r="C3536">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3536">
         <v>41</v>
@@ -61114,7 +61107,7 @@
         <v>84</v>
       </c>
       <c r="C3537">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3537">
         <v>41</v>
@@ -61131,7 +61124,7 @@
         <v>85</v>
       </c>
       <c r="C3538">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3538">
         <v>41</v>
@@ -61148,7 +61141,7 @@
         <v>85</v>
       </c>
       <c r="C3539">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3539">
         <v>41</v>
@@ -61182,7 +61175,7 @@
         <v>85</v>
       </c>
       <c r="C3541">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3541">
         <v>41</v>
@@ -61199,7 +61192,7 @@
         <v>85</v>
       </c>
       <c r="C3542">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3542">
         <v>41</v>
@@ -61216,7 +61209,7 @@
         <v>86</v>
       </c>
       <c r="C3543">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3543">
         <v>41</v>
@@ -61233,7 +61226,7 @@
         <v>86</v>
       </c>
       <c r="C3544">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3544">
         <v>41</v>
@@ -61267,7 +61260,7 @@
         <v>86</v>
       </c>
       <c r="C3546">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3546">
         <v>41</v>
@@ -61284,7 +61277,7 @@
         <v>86</v>
       </c>
       <c r="C3547">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3547">
         <v>41</v>
